--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,68 +425,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>last_message_date</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>last_response</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>response_status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>level_3_ai_response</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>subscription_checked</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>level_4_reminder_sent</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>decision</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>first_added_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6365338077</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xman1221</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-14T05:33:17.871136+00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,44 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>first_added_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1113695028</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Visionary_07</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-14T07:22:12.735752+00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +528,44 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7059362073</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arush23456</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -500,15 +500,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-14T05:33:17.871136+00:00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>2026-02-15T08:29:27.296272+00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes I am</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-15T08:29:27.296272+00:00</t>
+          <t>2026-02-15T10:53:38.508692+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes I am</t>
+          <t>Ok thanks 🙏</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -517,7 +517,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No worries</t>
+        </is>
+      </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,44 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5890041990</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yadavkunal97</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-15T10:53:38.508692+00:00</t>
+          <t>2026-02-16T11:38:42.053720+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,44 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1432292618</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>user_1432292618</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,6 +651,44 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5789748925</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Meoneeei</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,6 +689,44 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1207143648</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Initin_001</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,40 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1549816407</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>probably_pratyush</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,6 +764,40 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>962897168</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rampage519</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,40 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6660497489</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Helloooo_18</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,6 +832,40 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2115914497</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>user_2115914497</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,6 +866,40 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7626479674</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>user_7626479674</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,40 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7444482261</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Simran_thakur</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,40 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8620686461</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>alex_ggmongg</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,6 +968,40 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7178797837</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Popekrishna</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,6 +1002,40 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7289843412</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>user_7289843412</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,40 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1754739419</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cheezyycat</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1070,40 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2020153141</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>islayadmins</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,6 +1104,40 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6234770619</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>user_6234770619</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,40 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6597884456</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Promaster34666</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,40 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7915742060</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>user_7915742060</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,6 +1206,40 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7220761082</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WhoX0</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,40 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6477064253</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shubhi037</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1274,6 +1274,40 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6352388699</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>user_6352388699</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,6 +1308,40 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>924160594</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>user_924160594</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1342,6 +1342,40 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7339503030</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Phonix457</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1376,6 +1376,40 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8588937910</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>user_8588937910</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,6 +1410,40 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5350007972</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manu9752</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1444,40 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5089780638</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sanvi1803</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,6 +1478,40 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6243893394</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Princeshappylove</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,6 +1512,40 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8017866965</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>user_8017866965</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,6 +1546,40 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6150761678</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>kraryan07</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,6 +1580,40 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1224475627</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Londiyabaazcheems</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -550,9 +550,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-17T05:41:31.208872+00:00</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
@@ -588,9 +592,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-17T05:41:49.860251+00:00</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
@@ -664,9 +672,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-17T05:42:24.936199+00:00</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
@@ -702,9 +714,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-17T05:42:45.588433+00:00</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -714,17 +714,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-17T05:42:45.588433+00:00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>2026-03-17T07:01:27.283972+00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>What contacts?</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>unreachable</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -756,9 +760,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-17T06:59:59.287371+00:00</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -794,7 +802,11 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>0</v>
@@ -828,7 +840,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
         <v>0</v>
@@ -862,7 +878,11 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-17T07:01:27.283972+00:00</t>
+          <t>2026-03-17T07:59:57.367108+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>What contacts?</t>
+          <t>Im already there in this group I tried a few contacts but these are not updated many of the hRS have left the company</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -731,14 +731,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mostly outdated contacts, try searching again on company's website.</t>
+        </is>
+      </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Added during extraction</t>
@@ -916,7 +924,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -672,17 +672,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-17T05:42:24.936199+00:00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>2026-03-17T10:49:40.491375+00:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>yes I need job man!!!</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>unreachable</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-17T10:49:40.491375+00:00</t>
+          <t>2026-03-17T13:05:47.973484+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes I need job man!!!</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -689,14 +689,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Same here, done with OA</t>
+        </is>
+      </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Added during extraction</t>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -818,9 +818,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-17T19:54:58.128139+00:00</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
@@ -856,9 +860,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-17T19:55:18.929898+00:00</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -818,17 +818,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-17T19:54:58.128139+00:00</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>2026-03-17T20:36:52.411931+00:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>I am looking for switch Are they looking for experienced professionals?</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>unreachable</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -978,9 +982,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-17T20:35:56.663173+00:00</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1016,7 +1024,11 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1058,9 +1058,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-17T21:36:12.137502+00:00</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1100,7 +1100,11 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1702,6 +1702,40 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5551259677</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>user_5551259677</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1058,15 +1058,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-17T21:36:12.137502+00:00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>2026-03-18T06:59:50.752984+00:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yaa man looking</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1020,9 +1020,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-18T08:44:01.344999+00:00</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1146,9 +1146,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-18T09:51:48.935758+00:00</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1184,9 +1184,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-18T10:50:09.240840+00:00</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1222,9 +1222,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-18T11:43:54.385862+00:00</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1260,9 +1260,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-18T13:04:20.480717+00:00</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -1302,7 +1302,11 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>unreachable</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1768,40 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7908942533</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>user_7908942533</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -989,8 +989,16 @@
           <t>2026-03-17T20:35:56.663173+00:00</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1810,6 +1810,40 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2081315428</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sayani0603</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -982,11 +982,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-17T20:35:56.663173+00:00</t>
+          <t>2026-03-20T17:35:08.553796+00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1844,6 +1844,40 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5664055068</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OneNoughtOne101</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -787,8 +787,16 @@
           <t>2026-03-17T06:59:59.287371+00:00</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="b">
         <v>0</v>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1886,6 +1886,40 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>944036778</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>user_944036778</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -780,11 +780,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-17T06:59:59.287371+00:00</t>
+          <t>2026-03-22T06:47:48.188697+00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,6 +1920,40 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1751644983</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>seeyousoonokyes</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Added during extraction</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-17T20:36:52.411931+00:00</t>
+          <t>2026-04-12T12:57:25.584701+00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I am looking for switch Are they looking for experienced professionals?</t>
+          <t>Company name?</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -843,7 +843,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>"Microsoft."</t>
+        </is>
+      </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -826,11 +826,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-12T12:57:25.584701+00:00</t>
+          <t>2026-04-13T13:21:27.854224+00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -852,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -557,10 +557,14 @@
           <t>2026-03-17T05:41:31.208872+00:00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>unreachable</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -550,11 +550,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-17T05:41:31.208872+00:00</t>
+          <t>2026-05-18T22:59:08.620377+00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>

--- a/dm_promotion_service/data/users_engagement.xlsx
+++ b/dm_promotion_service/data/users_engagement.xlsx
@@ -550,31 +550,39 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18T22:59:08.620377+00:00</t>
+          <t>2026-05-19T00:08:46.073312+00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>Thnx buddy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No worries bro</t>
+        </is>
+      </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Added during extraction</t>
